--- a/deliverables/1784786903168-17720/AKKODiSマーケティングポータル_リニューアル提案書_清書版.xlsx
+++ b/deliverables/1784786903168-17720/AKKODiSマーケティングポータル_リニューアル提案書_清書版.xlsx
@@ -116,15 +116,15 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00001F33"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -354,14 +354,14 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -582,7 +582,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2190750" cy="2828925"/>
@@ -607,7 +607,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2190750" cy="7629525"/>
@@ -632,7 +632,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2190750" cy="3524250"/>
@@ -657,7 +657,7 @@
     <from>
       <col>10</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2190750" cy="2266950"/>
@@ -682,7 +682,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2190750" cy="1704975"/>
@@ -1367,7 +1367,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>個別ページではなく、5ページ全体に共通して現れる課題と、その対応方針をまとめています。</t>
         </is>
@@ -1661,7 +1661,7 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>前提：改善対象14課題とAI-1・AI-2の実装はマスト要件です（現状維持・対象外・良好・維持・要現物確認の8課題は設計を変更しません）。一部機能だけを先行して公開する進め方は採らず、1つのリリースとして同日カットオーバーで公開します。期間はいずれも目安であり、実際の所要はF0の確認結果と体制により変動します。</t>
         </is>
@@ -2117,7 +2117,7 @@
       </c>
     </row>
     <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>外部のアクセス解析ツールは利用できないため、SharePoint標準の「サイト利用状況（Site usage）」と「検索利用状況レポート（Search usage reports）」で測定します。検索利用状況レポートはサイトコレクション管理者のみが閲覧できるため、サイト所有者が自分で取得できるサイト利用状況を主軸に設計しています。AI-1とAI-2は取得可否が大きく異なるため、指標を分けています（#7・#8）。</t>
         </is>
@@ -2683,7 +2683,7 @@
       <c r="Q20" s="13" t="n"/>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>運用：刷新前にベースラインを取得→目標値を設定→公開後30日・90日で測定します。検索利用状況レポートは過去31日（日次）／12か月（月次）でExcel出力できます。AI-2の利用状況（#8）は取得可否そのものが未確認のため、F3の実機検証の結果に応じて本表を更新します。</t>
         </is>
@@ -2835,7 +2835,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>Microsoft公式ドキュメントで確認できた事項と、実機検証が必要な事項を分けて記載しています。</t>
         </is>
@@ -3091,7 +3091,7 @@
       <c r="N14" s="32" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>AI-1とAI-2は別のエージェントとして分離するのが妥当です。「文書検索の質問応答」と「ファイル解析＋ルール照合」で用途が大きく異なり、1つのエージェントに統合すると精度が落ちるためです。</t>
         </is>
@@ -3221,7 +3221,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>実装可否そのものに関わるリスク、および同日カットオーバー公開の前提を左右するリスクを優先して掲載しています。</t>
         </is>
@@ -3494,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4164,66 +4164,61 @@
       <c r="O26" s="19" t="n"/>
       <c r="P26" s="19" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>※ 解消14課題のうち B-7 と C-2 は、本構築の範囲では部分的な改善にとどまります。抜本的な整理は次フェーズで扱います（各課題の期待効果は課題一覧を参照）。</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
+      <c r="P27" s="13" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>4. 優先着手すべき課題トップ3</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
-      <c r="O28" s="9" t="n"/>
-      <c r="P28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="46" customHeight="1">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>B-1</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>ブランドライブラリの情報過多・ページ内ナビ欠如
 インパクト高／コスト中〜高。直近30日で最も使われる実働ページ（一意閲覧者319名）であり、「ガイドラインが増えてわかりにくい」という利用者の声に直接対応する。改善効果が最も広く届く。</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="46" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>G-2</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>ポータル内の検索性の弱さ
-インパクト高／コスト中〜高。「見つからないのでメールを探す」という状態の根本原因であり、AI-2導入の主戦場となる。</t>
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
@@ -4241,16 +4236,16 @@
       <c r="P30" s="6" t="n"/>
     </row>
     <row r="31" ht="46" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>C-1</t>
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>G-2</t>
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>クライアント向け「お役立ち資料」の30本超のリンク羅列
-インパクト高／コスト低〜中。説明文・分類・絞り込みがなく発見コストが高い。資料の並べ方をAI-2が回答根拠にできる形へ変えることで、検索性の改善と両立できる。</t>
+          <t>ポータル内の検索性の弱さ
+インパクト高／コスト中〜高。「見つからないのでメールを探す」という状態の根本原因であり、AI-2導入の主戦場となる。</t>
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
@@ -4267,54 +4262,59 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>クライアント向け「お役立ち資料」の30本超のリンク羅列
+インパクト高／コスト低〜中。説明文・分類・絞り込みがなく発見コストが高い。資料の並べ方をAI-2が回答根拠にできる形へ変えることで、検索性の改善と両立できる。</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>5. 改善方針</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="9" t="n"/>
-      <c r="N33" s="9" t="n"/>
-      <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="n"/>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>・改善対象14課題を SharePoint 標準Web パーツ（クイックリンク／テキスト／行動喚起／埋め込み 等）で実装し、追加ライセンスなしで実現できる範囲を中心に構築する。現状維持・対象外・良好・維持・要現物確認の8課題は設計を変更せず、区分として状態を明示する。</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>・AI-1（ブランドセルフチェッカー：Copilot Studio）／AI-2（マーケ特化AIアシスタント：SharePoint agent）の実装をマスト要件とし、一部機能だけを先行公開する進め方は採らない。</t>
+          <t>・改善対象14課題を SharePoint 標準Web パーツ（クイックリンク／テキスト／行動喚起／埋め込み 等）で実装し、追加ライセンスなしで実現できる範囲を中心に構築する。現状維持・対象外・良好・維持・要現物確認の8課題は設計を変更せず、区分として状態を明示する。</t>
         </is>
       </c>
       <c r="B35" s="13" t="n"/>
@@ -4336,7 +4336,7 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>・改善対象14課題とAI-1・AI-2を1つのリリースとしてまとめ、同日カットオーバーで公開する（フェーズ F0〜F4。詳細は「フェーズ計画」シート）。</t>
+          <t>・AI-1（ブランドセルフチェッカー：Copilot Studio）／AI-2（マーケ特化AIアシスタント：SharePoint agent）の実装をマスト要件とし、一部機能だけを先行公開する進め方は採らない。</t>
         </is>
       </c>
       <c r="B36" s="13" t="n"/>
@@ -4358,7 +4358,7 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>・AI-1・AI-2の前提となる M365 Copilot／Copilot Studio のライセンスと管理者許可の確認（F0）が最大のクリティカルパス。F0でライセンス・権限が確保できない場合は同日公開の前提が崩れるため、公開延期を原則とする。</t>
+          <t>・改善対象14課題とAI-1・AI-2を1つのリリースとしてまとめ、同日カットオーバーで公開する（フェーズ F0〜F4。詳細は「フェーズ計画」シート）。</t>
         </is>
       </c>
       <c r="B37" s="13" t="n"/>
@@ -4377,29 +4377,50 @@
       <c r="O37" s="13" t="n"/>
       <c r="P37" s="13" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>・AI-1・AI-2の前提となる M365 Copilot／Copilot Studio のライセンスと管理者許可の確認（F0）が最大のクリティカルパス。F0でライセンス・権限が確保できない場合は同日公開の前提が崩れるため、公開延期を原則とする。</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="13" t="n"/>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
+      <c r="P38" s="13" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>6. 全体像（ToBe ワイヤーフレーム 5ページ）</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
+    </row>
     <row r="42" ht="15" customHeight="1"/>
     <row r="43" ht="15" customHeight="1"/>
     <row r="44" ht="15" customHeight="1"/>
@@ -4443,57 +4464,58 @@
     <row r="82" ht="15" customHeight="1"/>
     <row r="83" ht="15" customHeight="1"/>
     <row r="84" ht="15" customHeight="1"/>
-    <row r="85">
-      <c r="B85" s="34" t="inlineStr">
+    <row r="85" ht="15" customHeight="1"/>
+    <row r="86">
+      <c r="B86" s="35" t="inlineStr">
         <is>
           <t>1. トップ（ホーム）</t>
         </is>
       </c>
-      <c r="E85" s="34" t="inlineStr">
+      <c r="E86" s="35" t="inlineStr">
         <is>
           <t>2. ブランドライブラリ</t>
         </is>
       </c>
-      <c r="H85" s="34" t="inlineStr">
+      <c r="H86" s="35" t="inlineStr">
         <is>
           <t>3. クライアント向け</t>
         </is>
       </c>
-      <c r="K85" s="34" t="inlineStr">
+      <c r="K86" s="35" t="inlineStr">
         <is>
           <t>4. キャンディデート向け</t>
         </is>
       </c>
-      <c r="N85" s="34" t="inlineStr">
+      <c r="N86" s="35" t="inlineStr">
         <is>
           <t>5. パートナー向け</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="12" t="inlineStr">
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="12" t="inlineStr">
         <is>
           <t>※各ページの構成と、セクションごとの設計意図は「WF 1.〜WF 5.」の各シートを参照してください。</t>
         </is>
       </c>
-      <c r="B87" s="13" t="n"/>
-      <c r="C87" s="13" t="n"/>
-      <c r="D87" s="13" t="n"/>
-      <c r="E87" s="13" t="n"/>
-      <c r="F87" s="13" t="n"/>
-      <c r="G87" s="13" t="n"/>
-      <c r="H87" s="13" t="n"/>
-      <c r="I87" s="13" t="n"/>
-      <c r="J87" s="13" t="n"/>
-      <c r="K87" s="13" t="n"/>
-      <c r="L87" s="13" t="n"/>
-      <c r="M87" s="13" t="n"/>
-      <c r="N87" s="13" t="n"/>
-      <c r="O87" s="13" t="n"/>
-      <c r="P87" s="13" t="n"/>
+      <c r="B88" s="13" t="n"/>
+      <c r="C88" s="13" t="n"/>
+      <c r="D88" s="13" t="n"/>
+      <c r="E88" s="13" t="n"/>
+      <c r="F88" s="13" t="n"/>
+      <c r="G88" s="13" t="n"/>
+      <c r="H88" s="13" t="n"/>
+      <c r="I88" s="13" t="n"/>
+      <c r="J88" s="13" t="n"/>
+      <c r="K88" s="13" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
+      <c r="N88" s="13" t="n"/>
+      <c r="O88" s="13" t="n"/>
+      <c r="P88" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="82">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="A20:D20"/>
@@ -4503,11 +4525,10 @@
     <mergeCell ref="A35:P35"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="A19:P19"/>
-    <mergeCell ref="A28:P28"/>
     <mergeCell ref="A9:P9"/>
-    <mergeCell ref="A39:P39"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="A24:D24"/>
+    <mergeCell ref="H86:J86"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H15:I15"/>
@@ -4517,32 +4538,34 @@
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="J12:P12"/>
+    <mergeCell ref="K86:M86"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="C29:P29"/>
+    <mergeCell ref="E86:G86"/>
     <mergeCell ref="A34:P34"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="C31:P31"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="A36:P36"/>
-    <mergeCell ref="B85:D85"/>
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A87:P87"/>
+    <mergeCell ref="N86:P86"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A37:P37"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C32:P32"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="A5:P5"/>
-    <mergeCell ref="K85:M85"/>
     <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A38:P38"/>
     <mergeCell ref="G22:P22"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A40:P40"/>
     <mergeCell ref="G21:P21"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="A12:B12"/>
@@ -4551,30 +4574,30 @@
     <mergeCell ref="G23:P23"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="N85:P85"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B86:D86"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="H85:J85"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="G20:P20"/>
     <mergeCell ref="G25:P25"/>
+    <mergeCell ref="A29:P29"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="J17:P17"/>
     <mergeCell ref="J10:P10"/>
-    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="A88:P88"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A7:P7"/>
     <mergeCell ref="C17:G17"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:P27"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="G24:P24"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A33:P33"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4643,7 +4666,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>区分は 解消／現状維持／対象外／良好・維持／要現物確認 の5つで、課題ごとに扱いを明示しています。「全22課題を解消」という一括表現は用いていません（区分別の件数はエグゼクティブサマリーを参照）。</t>
         </is>
@@ -5950,7 +5973,7 @@
       <c r="P3" s="30" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>左がワイヤーフレーム、右が各セクションへのコメントです。画像内の丸番号と右表の「No」が対応しています。ワイヤーフレームは構成を示すもので、文言・画像は実装時に確定します。</t>
         </is>
@@ -6100,7 +6123,7 @@
       </c>
       <c r="L12" s="51" t="inlineStr">
         <is>
-          <t>目次専用のWebパーツは提供されていないため、テキストWebパーツの見出しから自動生成されるページ内アンカーを、クイックリンクWebパーツで束ねて目次ブロックとして表現する。この目次パターンは全ページで共通とする。</t>
+          <t>目次専用のWebパーツは提供されていないため、テキスト Web パーツの見出しから自動生成されるページ内アンカーを、クイックリンク Web パーツで束ねて目次ブロックとして表現する。この目次パターンは全ページで共通とする。</t>
         </is>
       </c>
       <c r="M12" s="13" t="n"/>
@@ -6132,7 +6155,7 @@
       </c>
       <c r="L14" s="54" t="inlineStr">
         <is>
-          <t>各カードの直下に1行の説明文欄を設け、カードだけでは伝わらない遷移先の内容を補う。クイックリンクWebパーツはレスポンシブに4件を横並び表示できるため4列で配置する（3列までという制約はセクションの列レイアウトに適用されるもので、このパーツ自体には掛からない）。説明文の文面はマーケティング部で確定する。</t>
+          <t>各カードの直下に1行の説明文欄を設け、カードだけでは伝わらない遷移先の内容を補う。クイックリンク Web パーツはレスポンシブに4件を横並び表示できるため4列で配置する（3列までという制約はセクションの列レイアウトに適用されるもので、このパーツ自体には掛からない）。説明文の文面はマーケティング部で確定する。</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -6164,7 +6187,7 @@
       </c>
       <c r="L16" s="51" t="inlineStr">
         <is>
-          <t>①AI-1セルフチェック → ②手順ガイド → ③業務依頼フォーム を上から下へ全幅で並べる縦積みの導線とし、正式な依頼窓口はフォーム1つに統一する。①のAI-1（ブランドセルフチェッカー）はCopilot Studioで作成したエージェントを埋め込みWebパーツで設置し、アップロードした資料をブランドガイドラインと照合して一次スクリーニングの気づきを返す（色やロゴの厳密な判定は保証せず、最終承認は人が行う）。Copilot Studioのライセンス、PowerPointファイルのアップロード機能、認証なしのWebサイトチャネル公開の可否は、テナント管理者と実機検証で確認する。</t>
+          <t>①AI-1セルフチェック → ②手順ガイド → ③業務依頼フォーム を上から下へ全幅で並べる縦積みの導線とし、正式な依頼窓口はフォーム1つに統一する。①のAI-1（ブランドセルフチェッカー）はCopilot Studioで作成したエージェントを埋め込み Web パーツで設置し、アップロードした資料をブランドガイドラインと照合して一次スクリーニングの気づきを返す（色やロゴの厳密な判定は保証せず、最終承認は人が行う）。Copilot Studioのライセンス、PowerPointファイルのアップロード機能、認証なしのWebサイトチャネル公開の可否は、テナント管理者と実機検証で確認する。</t>
         </is>
       </c>
       <c r="M16" s="13" t="n"/>
@@ -6238,7 +6261,7 @@
     </row>
     <row r="21" ht="78.90000000000001" customHeight="1"/>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>※「該当課題」欄の「—」は、課題一覧に紐づく課題がなく、全ページ共通の設計として置くセクションであることを示します。</t>
         </is>
@@ -6389,7 +6412,7 @@
       <c r="P3" s="30" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>左がワイヤーフレーム、右が各セクションへのコメントです。画像内の丸番号と右表の「No」が対応しています。ワイヤーフレームは構成を示すもので、文言・画像は実装時に確定します。</t>
         </is>
@@ -6571,7 +6594,7 @@
       </c>
       <c r="L14" s="54" t="inlineStr">
         <is>
-          <t>レビュー依頼の対象範囲・提出物・所要日数の目安・依頼窓口を本文として記載する。セクションの背景色はセクション単位でのみ設定でき、テキストWebパーツ内の段落ごとに色を付ける機能はMicrosoft公式ドキュメントに記載がないため、案内トーンと注意喚起トーンの色分けはセクションを分けて実現する。AI-1（ブランドセルフチェッカー）はこのセクションに設置し、ロゴ掲載申請のセクションからは同じ導線を参照して二重に設置しない。</t>
+          <t>レビュー依頼の対象範囲・提出物・所要日数の目安・依頼窓口を本文として記載する。セクションの背景色はセクション単位でのみ設定でき、テキスト Web パーツ内の段落ごとに色を付ける機能はMicrosoft公式ドキュメントに記載がないため、案内トーンと注意喚起トーンの色分けはセクションを分けて実現する。AI-1（ブランドセルフチェッカー）はこのセクションに設置し、ロゴ掲載申請のセクションからは同じ導線を参照して二重に設置しない。</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -6635,7 +6658,7 @@
       </c>
       <c r="L18" s="54" t="inlineStr">
         <is>
-          <t>新規のドキュメントライブラリは作らず、目的軸の4カテゴリ見出しと既存資料へのリンク箇条書きをテキストWebパーツで表現する。情報量が多いためページは分割せず、「このセクションを折りたたみ可能にする」を有効にして既定は折りたたみ状態で格納する。リンクラベルの表記は「AKKODiS」に統一し、掲載前に既存ガイドラインの重複・旧版の棚卸しを運用作業として実施する。</t>
+          <t>新規のドキュメントライブラリは作らず、目的軸の4カテゴリ見出しと既存資料へのリンク箇条書きをテキスト Web パーツで表現する。情報量が多いためページは分割せず、「このセクションを折りたたみ可能にする」を有効にして既定は折りたたみ状態で格納する。リンクラベルの表記は「AKKODiS」に統一し、掲載前に既存ガイドラインの重複・旧版の棚卸しを運用作業として実施する。</t>
         </is>
       </c>
       <c r="M18" s="19" t="n"/>
@@ -6699,7 +6722,7 @@
       </c>
       <c r="L22" s="54" t="inlineStr">
         <is>
-          <t>ロゴ素材そのものは新規ライブラリを作らず、既存のロゴ素材ライブラリへのリンクをテキストWebパーツに並べる。手続きを扱う「ロゴ掲載申請」とは別のセクションである旨を本文に明記する。既存ライブラリの中身を一覧表示したい場合は、既存ライブラリを参照するドキュメント ライブラリ Web パーツを代替手段として使える。</t>
+          <t>ロゴ素材そのものは新規ライブラリを作らず、既存のロゴ素材ライブラリへのリンクをテキスト Web パーツに並べる。手続きを扱う「ロゴ掲載申請」とは別のセクションである旨を本文に明記する。既存ライブラリの中身を一覧表示したい場合は、既存ライブラリを参照するドキュメント ライブラリ Web パーツを代替手段として使える。</t>
         </is>
       </c>
       <c r="M22" s="19" t="n"/>
@@ -6795,7 +6818,7 @@
       </c>
       <c r="L28" s="51" t="inlineStr">
         <is>
-          <t>1つのテキストWebパーツの中に4つの見出しと各リンクの箇条書きを置き、クイックリンクWebパーツは併用しない。図中の2列表示はワイヤーフレーム上の便宜的な配置であり、セクションの列レイアウトを指定するものではない。</t>
+          <t>1つのテキスト Web パーツの中に4つの見出しと各リンクの箇条書きを置き、クイックリンク Web パーツは併用しない。図中の2列表示はワイヤーフレーム上の便宜的な配置であり、セクションの列レイアウトを指定するものではない。</t>
         </is>
       </c>
       <c r="M28" s="13" t="n"/>
@@ -6827,7 +6850,7 @@
       </c>
       <c r="L30" s="54" t="inlineStr">
         <is>
-          <t>5区分の見出しと実際のリンク件数（6／1／1／1／2件）を、テキストWebパーツ1つの中に見出し＋箇条書きで表現する。強調表示されたコンテンツWebパーツはサイトやライブラリ単位の動的クエリでファイル・ページを一覧表示するパーツで、個別のリンクを1件ずつ指定する少数のリンク集には使用しない。掲載する個々のリンク先はマーケティング部が確定する。</t>
+          <t>5区分の見出しと実際のリンク件数（6／1／1／1／2件）を、テキスト Web パーツ1つの中に見出し＋箇条書きで表現する。強調表示されたコンテンツ Web パーツはサイトやライブラリ単位の動的クエリでファイル・ページを一覧表示するパーツで、個別のリンクを1件ずつ指定する少数のリンク集には使用しない。掲載する個々のリンク先はマーケティング部が確定する。</t>
         </is>
       </c>
       <c r="M30" s="19" t="n"/>
@@ -6859,7 +6882,7 @@
       </c>
       <c r="L32" s="51" t="inlineStr">
         <is>
-          <t>3件のリンクは見出しが長いため、クイックリンクWebパーツではなくテキストWebパーツのリンク付き箇条書きで表現する。クイックリンクの見出し文字数の上限は公開情報に数値の記載がないため、実機検証で確認する。</t>
+          <t>3件のリンクは見出しが長いため、クイックリンク Web パーツではなくテキスト Web パーツのリンク付き箇条書きで表現する。クイックリンクの見出し文字数の上限は公開情報に数値の記載がないため、実機検証で確認する。</t>
         </is>
       </c>
       <c r="M32" s="13" t="n"/>
@@ -6901,7 +6924,7 @@
     </row>
     <row r="35" ht="79.8" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>※「該当課題」欄の「—」は、課題一覧に紐づく課題がなく、全ページ共通の設計として置くセクションであることを示します。</t>
         </is>
@@ -7087,7 +7110,7 @@
       <c r="P3" s="30" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>左がワイヤーフレーム、右が各セクションへのコメントです。画像内の丸番号と右表の「No」が対応しています。ワイヤーフレームは構成を示すもので、文言・画像は実装時に確定します。</t>
         </is>
@@ -7269,7 +7292,7 @@
       </c>
       <c r="L14" s="54" t="inlineStr">
         <is>
-          <t>セミナー・活用事例・AKKODiS Insights・サービスページの4つを現行の内容のまま並べる。クイックリンクWebパーツはレスポンシブに4件を横並び表示できるため4列で配置する。</t>
+          <t>セミナー・活用事例・AKKODiS Insights・サービスページの4つを現行の内容のまま並べる。クイックリンク Web パーツはレスポンシブに4件を横並び表示できるため4列で配置する。</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -7301,7 +7324,7 @@
       </c>
       <c r="L16" s="51" t="inlineStr">
         <is>
-          <t>主案は、カテゴリ見出しと資料リンクの箇条書きをテキストWebパーツで表現し（掲載するのは資料へのリンクでありファイル実体ではない。更新日の記載は任意）、30本を超えるお役立ち資料は折りたたみセクションに格納する。SharePoint agentが回答の根拠に使えるのはページ本文とドキュメントライブラリで、リストのデータは対象外だとMicrosoft公式ドキュメントに明記されているため、資料リンクはページ本文に置く。点線枠の副案は、カテゴリ・言語・更新日の列とビューによる絞り込みを人が使うための補助としてリストWebパーツを併設する案で、主案が持たない動的な絞り込みを補える一方、エージェントの回答根拠にはならない。</t>
+          <t>主案は、カテゴリ見出しと資料リンクの箇条書きをテキスト Web パーツで表現し（掲載するのは資料へのリンクでありファイル実体ではない。更新日の記載は任意）、30本を超えるお役立ち資料は折りたたみセクションに格納する。SharePoint agentが回答の根拠に使えるのはページ本文とドキュメントライブラリで、リストのデータは対象外だとMicrosoft公式ドキュメントに明記されているため、資料リンクはページ本文に置く。点線枠の副案は、カテゴリ・言語・更新日の列とビューによる絞り込みを人が使うための補助としてリスト Web パーツを併設する案で、主案が持たない動的な絞り込みを補える一方、エージェントの回答根拠にはならない。</t>
         </is>
       </c>
       <c r="M16" s="13" t="n"/>
@@ -7344,7 +7367,7 @@
     </row>
     <row r="20" ht="92.40000000000001" customHeight="1"/>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>※「該当課題」欄の「—」は、課題一覧に紐づく課題がなく、全ページ共通の設計として置くセクションであることを示します。</t>
         </is>
@@ -7490,7 +7513,7 @@
       <c r="P3" s="30" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>左がワイヤーフレーム、右が各セクションへのコメントです。画像内の丸番号と右表の「No」が対応しています。ワイヤーフレームは構成を示すもので、文言・画像は実装時に確定します。</t>
         </is>
@@ -7672,7 +7695,7 @@
       </c>
       <c r="L14" s="54" t="inlineStr">
         <is>
-          <t>「AKKODiS People」は、説明文と複数のハイパーリンク（採用サイトへのリンク、告知投稿の依頼はマーケへの業務依頼フォームへ）をテキストWebパーツで表現する。クイックリンクWebパーツは1タイルにつき1リンクという構成で、1つのタイルに副リンクを追加する設定項目が存在しないため、副リンクが必要なブロックにはテキストWebパーツを使う。「リクルーティングムービー」は1タイル1リンクのクイックリンクWebパーツのまま維持する。</t>
+          <t>「AKKODiS People」は、説明文と複数のハイパーリンク（採用サイトへのリンク、告知投稿の依頼はマーケへの業務依頼フォームへ）をテキスト Web パーツで表現する。クイックリンク Web パーツは1タイルにつき1リンクという構成で、1つのタイルに副リンクを追加する設定項目が存在しないため、副リンクが必要なブロックにはテキスト Web パーツを使う。「リクルーティングムービー」は1タイル1リンクのクイックリンク Web パーツのまま維持する。</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -7704,7 +7727,7 @@
       </c>
       <c r="L16" s="51" t="inlineStr">
         <is>
-          <t>会社説明資料は各チームが管理しているため、現行の案内文をそのままテキストWebパーツに掲載し、資料への直リンク化は行わない。中途採用・新卒採用・障がい者採用の3チームの連絡先を現行どおり併記する。</t>
+          <t>会社説明資料は各チームが管理しているため、現行の案内文をそのままテキスト Web パーツに掲載し、資料への直リンク化は行わない。中途採用・新卒採用・障がい者採用の3チームの連絡先を現行どおり併記する。</t>
         </is>
       </c>
       <c r="M16" s="13" t="n"/>
@@ -7746,7 +7769,7 @@
     </row>
     <row r="19" ht="119.4" customHeight="1"/>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>※「該当課題」欄の「—」は、課題一覧に紐づく課題がなく、全ページ共通の設計として置くセクションであることを示します。</t>
         </is>
@@ -7892,7 +7915,7 @@
       <c r="P3" s="30" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>左がワイヤーフレーム、右が各セクションへのコメントです。画像内の丸番号と右表の「No」が対応しています。ワイヤーフレームは構成を示すもので、文言・画像は実装時に確定します。</t>
         </is>
@@ -8116,7 +8139,7 @@
     </row>
     <row r="17" ht="92.09999999999999" customHeight="1"/>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>※「該当課題」欄の「—」は、課題一覧に紐づく課題がなく、全ページ共通の設計として置くセクションであることを示します。</t>
         </is>
@@ -8231,7 +8254,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>クライアント向けページの公開資料を、①テキストのみ／②テキスト＋リスト併用／③リストのみ の3構成で比較します。AI-1・AI-2の実装がマスト要件であるため、「AI-2が資料リンクを回答根拠にできるか」を最重要の判断軸としています。</t>
         </is>
@@ -8663,7 +8686,7 @@
       <c r="N20" s="32" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>将来、リストがSharePoint agentのナレッジソースとして正式に対応された場合は、この比較を見直す価値があります。本書時点のMicrosoft公式ドキュメントでは未対応です。</t>
         </is>
